--- a/Pokemon_Dashboard/Pokemon_Images.xlsx
+++ b/Pokemon_Dashboard/Pokemon_Images.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ygiduturi\Documents\Power BI Dashboards\Datasets\Pokemon\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yeswa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5863430-20CE-45FA-A631-381826A70426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3CC35B-5643-436A-ADA2-EAC62EB7C2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="814">
   <si>
     <t>#</t>
   </si>
@@ -2458,6 +2458,15 @@
   </si>
   <si>
     <t>https://th.bing.com/th/id/OIP.LyiEm_utOyvINX997clyRQAAAA?rs=1&amp;pid=ImgDetMain</t>
+  </si>
+  <si>
+    <t>Nothing</t>
+  </si>
+  <si>
+    <t>https://img.freepik.com/free-vector/vector-damask-seamless-pattern-background-classical-luxury-old-fashioned-damask-ornament-royal-victorian-seamless-texture-wallpapers-textile-wrapping-exquisite-floral-baroque-template_1217-738.jpg</t>
+  </si>
+  <si>
+    <t>https://lh6.googleusercontent.com/fRqq968jAGtKCb7ScboyPZGMsgEBkPvpZ0A0anACqqN3XGKzYZ72_kOptPisrdbKlkc5ORt4A4vzIkvR81hfmYD0cf9L3qUDRWYJDnpxzXE7g5t9QA-kMxnV4Wz7XO58PL9p66pt</t>
   </si>
 </sst>
 </file>
@@ -2786,7 +2795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C801"/>
+  <dimension ref="A1:C802"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.33203125" customWidth="1"/>
@@ -5117,7 +5126,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>264</v>
       </c>
@@ -5125,7 +5134,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>265</v>
       </c>
@@ -5133,7 +5142,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>266</v>
       </c>
@@ -5141,7 +5150,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>267</v>
       </c>
@@ -5149,7 +5158,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>268</v>
       </c>
@@ -5157,7 +5166,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>269</v>
       </c>
@@ -5165,7 +5174,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>270</v>
       </c>
@@ -5173,15 +5182,18 @@
         <v>295</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>271</v>
       </c>
       <c r="B296" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C296" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>272</v>
       </c>
@@ -5189,7 +5201,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>273</v>
       </c>
@@ -5197,7 +5209,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>274</v>
       </c>
@@ -5205,7 +5217,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>275</v>
       </c>
@@ -5213,7 +5225,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>276</v>
       </c>
@@ -5221,7 +5233,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>277</v>
       </c>
@@ -5229,7 +5241,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>278</v>
       </c>
@@ -5237,7 +5249,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>279</v>
       </c>
@@ -9219,12 +9231,23 @@
         <v>800</v>
       </c>
     </row>
-    <row r="801" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A801">
         <v>721</v>
       </c>
       <c r="B801" t="s">
         <v>801</v>
+      </c>
+    </row>
+    <row r="802" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A802">
+        <v>723</v>
+      </c>
+      <c r="B802" t="s">
+        <v>811</v>
+      </c>
+      <c r="C802" s="1" t="s">
+        <v>812</v>
       </c>
     </row>
   </sheetData>
@@ -9237,6 +9260,8 @@
     <hyperlink ref="C8" r:id="rId6" xr:uid="{2849EA09-AD06-4082-8401-D015AB2E2612}"/>
     <hyperlink ref="C439" r:id="rId7" xr:uid="{ACD72061-C8D5-4100-8C75-D79E10314C71}"/>
     <hyperlink ref="C59" r:id="rId8" xr:uid="{1380A957-2563-44F8-A5A0-240683BFAEA2}"/>
+    <hyperlink ref="C802" r:id="rId9" xr:uid="{AB01FFD3-0116-45A9-AA83-771ED23B0665}"/>
+    <hyperlink ref="C296" r:id="rId10" xr:uid="{738C56A7-1FEE-484E-BBF8-8E925E4BF8A0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
